--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:L31"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,7 +413,7 @@
         <v>תאריך סריקה</v>
       </c>
       <c r="E1" t="str">
-        <v>תיאור</v>
+        <v>שעה</v>
       </c>
       <c r="F1" t="str">
         <v>משך</v>
@@ -442,7 +442,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-22</v>
@@ -457,15 +457,18 @@
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>שמואל חי מעודה - ארוממך להורדה</v>
       </c>
     </row>
@@ -477,7 +480,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-22</v>
@@ -492,15 +495,18 @@
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>שירה זלוף - לא אוהבת סרטים להורדה</v>
       </c>
     </row>
@@ -512,7 +518,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-22</v>
@@ -527,15 +533,18 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v>שי נחייסי - הלב שלם להורדה</v>
       </c>
     </row>
@@ -547,7 +556,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-22</v>
@@ -562,15 +571,18 @@
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v>שובל בבייב - כמו ציפור להורדה</v>
       </c>
     </row>
@@ -582,7 +594,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-22</v>
@@ -597,15 +609,18 @@
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v>רן דנקר - תמונת מצב להורדה</v>
       </c>
     </row>
@@ -617,7 +632,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-22</v>
@@ -632,15 +647,18 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v>פייגה סבג - שוב לבד להורדה</v>
       </c>
     </row>
@@ -652,7 +670,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D8" t="str">
         <v>2026-01-22</v>
@@ -667,15 +685,18 @@
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v>פארידה - מחרוזת פארידה 2026 להורדה</v>
       </c>
     </row>
@@ -687,7 +708,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D9" t="str">
         <v>2026-01-22</v>
@@ -702,15 +723,18 @@
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v>נתי קוריטרו - תחנה בזמן להורדה</v>
       </c>
     </row>
@@ -722,7 +746,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D10" t="str">
         <v>2026-01-22</v>
@@ -737,15 +761,18 @@
         <v/>
       </c>
       <c r="H10" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v>מושיקו מזרחי - כמו בחלום להורדה</v>
       </c>
     </row>
@@ -757,7 +784,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D11" t="str">
         <v>2026-01-22</v>
@@ -772,15 +799,18 @@
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v>מושיקו מזרחי - זמר בפאן להורדה</v>
       </c>
     </row>
@@ -792,7 +822,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D12" t="str">
         <v>2026-01-22</v>
@@ -807,15 +837,18 @@
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v>מושיקו מזרחי - הכל מכתוב להורדה</v>
       </c>
     </row>
@@ -827,7 +860,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D13" t="str">
         <v>2026-01-22</v>
@@ -842,15 +875,18 @@
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v>יניב מדר - להילולה קאבר להורדה</v>
       </c>
     </row>
@@ -862,7 +898,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D14" t="str">
         <v>2026-01-22</v>
@@ -877,15 +913,18 @@
         <v/>
       </c>
       <c r="H14" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v>יואב זלדין - טייס חופשי להורדה</v>
       </c>
     </row>
@@ -897,7 +936,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D15" t="str">
         <v>2026-01-22</v>
@@ -912,15 +951,18 @@
         <v/>
       </c>
       <c r="H15" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
         <v>יגל יובל שרעבי - שקרן מוסמך להורדה</v>
       </c>
     </row>
@@ -932,7 +974,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D16" t="str">
         <v>2026-01-22</v>
@@ -947,15 +989,18 @@
         <v/>
       </c>
       <c r="H16" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
         <v>דה לוי - אול אין להורדה</v>
       </c>
     </row>
@@ -967,7 +1012,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D17" t="str">
         <v>2026-01-22</v>
@@ -982,15 +1027,18 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
         <v>גל טייב - לפני הזריחה להורדה</v>
       </c>
     </row>
@@ -1002,7 +1050,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D18" t="str">
         <v>2026-01-22</v>
@@ -1017,15 +1065,18 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v>גיא בן שמעון - אני מפחד וזה בסדר להורדה</v>
       </c>
     </row>
@@ -1037,7 +1088,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D19" t="str">
         <v>2026-01-22</v>
@@ -1052,15 +1103,18 @@
         <v/>
       </c>
       <c r="H19" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v>אמיר שדה - גופיית כדורסל להורדה</v>
       </c>
     </row>
@@ -1072,7 +1126,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D20" t="str">
         <v>2026-01-22</v>
@@ -1087,15 +1141,18 @@
         <v/>
       </c>
       <c r="H20" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v>אלמוג זגרון - מה זה בית להורדה</v>
       </c>
     </row>
@@ -1107,7 +1164,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D21" t="str">
         <v>2026-01-22</v>
@@ -1122,15 +1179,18 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v>אוריה - להיות באמת להורדה</v>
       </c>
     </row>
@@ -1142,7 +1202,7 @@
         <v>2026-01-22</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D22" t="str">
         <v>2026-01-22</v>
@@ -1157,15 +1217,18 @@
         <v/>
       </c>
       <c r="H22" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
       </c>
     </row>
@@ -1177,7 +1240,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D23" t="str">
         <v>2026-01-22</v>
@@ -1192,15 +1255,18 @@
         <v/>
       </c>
       <c r="H23" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v>שירז לביא - נראה לי זה הסוף להורדה</v>
       </c>
     </row>
@@ -1212,7 +1278,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D24" t="str">
         <v>2026-01-22</v>
@@ -1227,15 +1293,18 @@
         <v/>
       </c>
       <c r="H24" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v>ראובן המלאך - תגידי מה עובר עלייך להורדה</v>
       </c>
     </row>
@@ -1247,7 +1316,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D25" t="str">
         <v>2026-01-22</v>
@@ -1262,15 +1331,18 @@
         <v/>
       </c>
       <c r="H25" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v>עידו ביטון - היום יוצאים להורדה</v>
       </c>
     </row>
@@ -1282,7 +1354,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D26" t="str">
         <v>2026-01-22</v>
@@ -1297,15 +1369,18 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v>מור זיו - השער נפתח להורדה</v>
       </c>
     </row>
@@ -1317,7 +1392,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D27" t="str">
         <v>2026-01-22</v>
@@ -1332,15 +1407,18 @@
         <v/>
       </c>
       <c r="H27" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026 להורדה</v>
       </c>
     </row>
@@ -1352,7 +1430,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D28" t="str">
         <v>2026-01-22</v>
@@ -1367,15 +1445,18 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I28" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים להורדה</v>
       </c>
     </row>
@@ -1387,7 +1468,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D29" t="str">
         <v>2026-01-22</v>
@@ -1402,15 +1483,18 @@
         <v/>
       </c>
       <c r="H29" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I29" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v>ג'ולייטה - מי יציל אותי להורדה</v>
       </c>
     </row>
@@ -1422,7 +1506,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D30" t="str">
         <v>2026-01-22</v>
@@ -1437,15 +1521,18 @@
         <v/>
       </c>
       <c r="H30" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I30" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J30" t="str">
         <v/>
       </c>
       <c r="K30" t="str">
+        <v/>
+      </c>
+      <c r="L30" t="str">
         <v>אמיתי צדוק - במנורה אני נשבע להורדה</v>
       </c>
     </row>
@@ -1457,7 +1544,7 @@
         <v>2026-01-21</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=ba96c4ea19a5e1642a755de6f6e18269</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
       </c>
       <c r="D31" t="str">
         <v>2026-01-22</v>
@@ -1472,21 +1559,24 @@
         <v/>
       </c>
       <c r="H31" t="str">
-        <v>סינגלים חדשים</v>
+        <v/>
       </c>
       <c r="I31" t="str">
-        <v/>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J31" t="str">
         <v/>
       </c>
       <c r="K31" t="str">
+        <v/>
+      </c>
+      <c r="L31" t="str">
         <v>איתי דלומי - שיר היונה להורדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L31"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמואל חי מעודה - ארוממך להורדה</v>
+        <v>שמואל חי מעודה - ארוממך</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמואל חי מעודה - ארוממך להורדה</v>
+        <v>שמואל חי מעודה - ארוממך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שירה זלוף - לא אוהבת סרטים להורדה</v>
+        <v>שירה זלוף - לא אוהבת סרטים</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שירה זלוף - לא אוהבת סרטים להורדה</v>
+        <v>שירה זלוף - לא אוהבת סרטים</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שי נחייסי - הלב שלם להורדה</v>
+        <v>שי נחייסי - הלב שלם</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שי נחייסי - הלב שלם להורדה</v>
+        <v>שי נחייסי - הלב שלם</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שובל בבייב - כמו ציפור להורדה</v>
+        <v>שובל בבייב - כמו ציפור</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שובל בבייב - כמו ציפור להורדה</v>
+        <v>שובל בבייב - כמו ציפור</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רן דנקר - תמונת מצב להורדה</v>
+        <v>רן דנקר - תמונת מצב</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רן דנקר - תמונת מצב להורדה</v>
+        <v>רן דנקר - תמונת מצב</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פייגה סבג - שוב לבד להורדה</v>
+        <v>פייגה סבג - שוב לבד</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>פייגה סבג - שוב לבד להורדה</v>
+        <v>פייגה סבג - שוב לבד</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פארידה - מחרוזת פארידה 2026 להורדה</v>
+        <v>פארידה - מחרוזת פארידה 2026</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>פארידה - מחרוזת פארידה 2026 להורדה</v>
+        <v>פארידה - מחרוזת פארידה 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נתי קוריטרו - תחנה בזמן להורדה</v>
+        <v>נתי קוריטרו - תחנה בזמן</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נתי קוריטרו - תחנה בזמן להורדה</v>
+        <v>נתי קוריטרו - תחנה בזמן</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מושיקו מזרחי - כמו בחלום להורדה</v>
+        <v>מושיקו מזרחי - כמו בחלום</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>מושיקו מזרחי - כמו בחלום להורדה</v>
+        <v>מושיקו מזרחי - כמו בחלום</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>מושיקו מזרחי - זמר בפאן להורדה</v>
+        <v>מושיקו מזרחי - זמר בפאן</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>מושיקו מזרחי - זמר בפאן להורדה</v>
+        <v>מושיקו מזרחי - זמר בפאן</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>מושיקו מזרחי - הכל מכתוב להורדה</v>
+        <v>מושיקו מזרחי - הכל מכתוב</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>מושיקו מזרחי - הכל מכתוב להורדה</v>
+        <v>מושיקו מזרחי - הכל מכתוב</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>יניב מדר - להילולה קאבר להורדה</v>
+        <v>יניב מדר - להילולה קאבר</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>יניב מדר - להילולה קאבר להורדה</v>
+        <v>יניב מדר - להילולה קאבר</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>יואב זלדין - טייס חופשי להורדה</v>
+        <v>יואב זלדין - טייס חופשי</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>יואב זלדין - טייס חופשי להורדה</v>
+        <v>יואב זלדין - טייס חופשי</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>יגל יובל שרעבי - שקרן מוסמך להורדה</v>
+        <v>יגל יובל שרעבי - שקרן מוסמך</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>יגל יובל שרעבי - שקרן מוסמך להורדה</v>
+        <v>יגל יובל שרעבי - שקרן מוסמך</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דה לוי - אול אין להורדה</v>
+        <v>דה לוי - אול אין</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>דה לוי - אול אין להורדה</v>
+        <v>דה לוי - אול אין</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>גל טייב - לפני הזריחה להורדה</v>
+        <v>גל טייב - לפני הזריחה</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>גל טייב - לפני הזריחה להורדה</v>
+        <v>גל טייב - לפני הזריחה</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>גיא בן שמעון - אני מפחד וזה בסדר להורדה</v>
+        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>גיא בן שמעון - אני מפחד וזה בסדר להורדה</v>
+        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אמיר שדה - גופיית כדורסל להורדה</v>
+        <v>אמיר שדה - גופיית כדורסל</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>אמיר שדה - גופיית כדורסל להורדה</v>
+        <v>אמיר שדה - גופיית כדורסל</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אלמוג זגרון - מה זה בית להורדה</v>
+        <v>אלמוג זגרון - מה זה בית</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>אלמוג זגרון - מה זה בית להורדה</v>
+        <v>אלמוג זגרון - מה זה בית</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אוריה - להיות באמת להורדה</v>
+        <v>אוריה - להיות באמת</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1191,7 +1191,7 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>אוריה - להיות באמת להורדה</v>
+        <v>אוריה - להיות באמת</v>
       </c>
     </row>
     <row r="22">
@@ -1202,10 +1202,10 @@
         <v>2026-01-22</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1234,16 +1234,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>שירז לביא - נראה לי זה הסוף להורדה</v>
+        <v>שירז לביא - נראה לי זה הסוף</v>
       </c>
       <c r="B23" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>שירז לביא - נראה לי זה הסוף להורדה</v>
+        <v>שירז לביא - נראה לי זה הסוף</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ראובן המלאך - תגידי מה עובר עלייך להורדה</v>
+        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>ראובן המלאך - תגידי מה עובר עלייך להורדה</v>
+        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>עידו ביטון - היום יוצאים להורדה</v>
+        <v>עידו ביטון - היום יוצאים</v>
       </c>
       <c r="B25" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>עידו ביטון - היום יוצאים להורדה</v>
+        <v>עידו ביטון - היום יוצאים</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>מור זיו - השער נפתח להורדה</v>
+        <v>מור זיו - השער נפתח</v>
       </c>
       <c r="B26" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>מור זיו - השער נפתח להורדה</v>
+        <v>מור זיו - השער נפתח</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026 להורדה</v>
+        <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026</v>
       </c>
       <c r="B27" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026 להורדה</v>
+        <v>ישראל סוסנה וחברים - מחרוזת ראש חודש שמח 2026</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים להורדה</v>
+        <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים</v>
       </c>
       <c r="B28" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1457,21 +1457,21 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים להורדה</v>
+        <v>הרצף הגנטי מארח את אלעד עמדי - חוזר אל הדרכים</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ג'ולייטה - מי יציל אותי להורדה</v>
+        <v>ג'ולייטה - מי יציל אותי</v>
       </c>
       <c r="B29" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1495,21 +1495,21 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>ג'ולייטה - מי יציל אותי להורדה</v>
+        <v>ג'ולייטה - מי יציל אותי</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>אמיתי צדוק - במנורה אני נשבע להורדה</v>
+        <v>אמיתי צדוק - במנורה אני נשבע</v>
       </c>
       <c r="B30" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1533,21 +1533,21 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>אמיתי צדוק - במנורה אני נשבע להורדה</v>
+        <v>אמיתי צדוק - במנורה אני נשבע</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>איתי דלומי - שיר היונה להורדה</v>
+        <v>איתי דלומי - שיר היונה</v>
       </c>
       <c r="B31" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=00df79d04ec81e1adefc75b6c4577b0f</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -1571,7 +1571,7 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>איתי דלומי - שיר היונה להורדה</v>
+        <v>איתי דלומי - שיר היונה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמואל חי מעודה - ארוממך</v>
+        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמואל חי מעודה - ארוממך</v>
+        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שירה זלוף - לא אוהבת סרטים</v>
+        <v>שמואל חי מעודה - ארוממך</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-22</v>
+        <v>2026-01-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409328&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שירה זלוף - לא אוהבת סרטים</v>
+        <v>שמואל חי מעודה - ארוממך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שי נחייסי - הלב שלם</v>
+        <v>שירה זלוף - לא אוהבת סרטים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409327&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שי נחייסי - הלב שלם</v>
+        <v>שירה זלוף - לא אוהבת סרטים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שובל בבייב - כמו ציפור</v>
+        <v>שי נחייסי - הלב שלם</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409326&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שובל בבייב - כמו ציפור</v>
+        <v>שי נחייסי - הלב שלם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>רן דנקר - תמונת מצב</v>
+        <v>שובל בבייב - כמו ציפור</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409325&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>רן דנקר - תמונת מצב</v>
+        <v>שובל בבייב - כמו ציפור</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>פייגה סבג - שוב לבד</v>
+        <v>רן דנקר - תמונת מצב</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409324&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>פייגה סבג - שוב לבד</v>
+        <v>רן דנקר - תמונת מצב</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>פארידה - מחרוזת פארידה 2026</v>
+        <v>פייגה סבג - שוב לבד</v>
       </c>
       <c r="B8" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409323&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>פארידה - מחרוזת פארידה 2026</v>
+        <v>פייגה סבג - שוב לבד</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>נתי קוריטרו - תחנה בזמן</v>
+        <v>פארידה - מחרוזת פארידה 2026</v>
       </c>
       <c r="B9" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409322&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>נתי קוריטרו - תחנה בזמן</v>
+        <v>פארידה - מחרוזת פארידה 2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>מושיקו מזרחי - כמו בחלום</v>
+        <v>נתי קוריטרו - תחנה בזמן</v>
       </c>
       <c r="B10" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409321&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>מושיקו מזרחי - כמו בחלום</v>
+        <v>נתי קוריטרו - תחנה בזמן</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>מושיקו מזרחי - זמר בפאן</v>
+        <v>מושיקו מזרחי - כמו בחלום</v>
       </c>
       <c r="B11" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409320&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>מושיקו מזרחי - זמר בפאן</v>
+        <v>מושיקו מזרחי - כמו בחלום</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>מושיקו מזרחי - הכל מכתוב</v>
+        <v>מושיקו מזרחי - זמר בפאן</v>
       </c>
       <c r="B12" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409319&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,21 +849,21 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>מושיקו מזרחי - הכל מכתוב</v>
+        <v>מושיקו מזרחי - זמר בפאן</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>יניב מדר - להילולה קאבר</v>
+        <v>מושיקו מזרחי - הכל מכתוב</v>
       </c>
       <c r="B13" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409318&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -887,21 +887,21 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>יניב מדר - להילולה קאבר</v>
+        <v>מושיקו מזרחי - הכל מכתוב</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>יואב זלדין - טייס חופשי</v>
+        <v>יניב מדר - להילולה קאבר</v>
       </c>
       <c r="B14" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409317&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -925,21 +925,21 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>יואב זלדין - טייס חופשי</v>
+        <v>יניב מדר - להילולה קאבר</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>יגל יובל שרעבי - שקרן מוסמך</v>
+        <v>יואב זלדין - טייס חופשי</v>
       </c>
       <c r="B15" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409316&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -963,21 +963,21 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>יגל יובל שרעבי - שקרן מוסמך</v>
+        <v>יואב זלדין - טייס חופשי</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>דה לוי - אול אין</v>
+        <v>יגל יובל שרעבי - שקרן מוסמך</v>
       </c>
       <c r="B16" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409315&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>דה לוי - אול אין</v>
+        <v>יגל יובל שרעבי - שקרן מוסמך</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>גל טייב - לפני הזריחה</v>
+        <v>דה לוי - אול אין</v>
       </c>
       <c r="B17" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C17" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409314&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>גל טייב - לפני הזריחה</v>
+        <v>דה לוי - אול אין</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
+        <v>גל טייב - לפני הזריחה</v>
       </c>
       <c r="B18" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C18" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409313&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1077,21 +1077,21 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
+        <v>גל טייב - לפני הזריחה</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>אמיר שדה - גופיית כדורסל</v>
+        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
       </c>
       <c r="B19" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C19" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409312&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>אמיר שדה - גופיית כדורסל</v>
+        <v>גיא בן שמעון - אני מפחד וזה בסדר</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>אלמוג זגרון - מה זה בית</v>
+        <v>אמיר שדה - גופיית כדורסל</v>
       </c>
       <c r="B20" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C20" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409311&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>אלמוג זגרון - מה זה בית</v>
+        <v>אמיר שדה - גופיית כדורסל</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>אוריה - להיות באמת</v>
+        <v>אלמוג זגרון - מה זה בית</v>
       </c>
       <c r="B21" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C21" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409310&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>אוריה - להיות באמת</v>
+        <v>אלמוג זגרון - מה זה בית</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
+        <v>אוריה - להיות באמת</v>
       </c>
       <c r="B22" t="str">
         <v>2026-01-22</v>
       </c>
       <c r="C22" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409309&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
+        <v>אוריה - להיות באמת</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>שירז לביא - נראה לי זה הסוף</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
       </c>
       <c r="B23" t="str">
-        <v>2026-01-21</v>
+        <v>2026-01-22</v>
       </c>
       <c r="C23" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409308&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>שירז לביא - נראה לי זה הסוף</v>
+        <v>אבי ריימי &amp; יאיר בודנר מארחים את אברימי רוט - מִזְמוֹר שִׁיר</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
+        <v>שירז לביא - נראה לי זה הסוף</v>
       </c>
       <c r="B24" t="str">
         <v>2026-01-21</v>
       </c>
       <c r="C24" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409306&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409307&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1305,7 +1305,7 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>ראובן המלאך - תגידי מה עובר עלייך</v>
+        <v>שירז לביא - נראה לי זה הסוף</v>
       </c>
     </row>
     <row r="25">
@@ -1316,10 +1316,10 @@
         <v>2026-01-21</v>
       </c>
       <c r="C25" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409305&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1354,10 +1354,10 @@
         <v>2026-01-21</v>
       </c>
       <c r="C26" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409304&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1392,10 +1392,10 @@
         <v>2026-01-21</v>
       </c>
       <c r="C27" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409303&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1430,10 +1430,10 @@
         <v>2026-01-21</v>
       </c>
       <c r="C28" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409302&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1468,10 +1468,10 @@
         <v>2026-01-21</v>
       </c>
       <c r="C29" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409301&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -1506,10 +1506,10 @@
         <v>2026-01-21</v>
       </c>
       <c r="C30" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409300&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -1544,10 +1544,10 @@
         <v>2026-01-21</v>
       </c>
       <c r="C31" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=4d0da7a4620ddb18105d45b5903d0e61</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409299&amp;sid=6d099aab60b87627cc5097d567401bf4</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-01-23</v>
+        <v>2026-01-24</v>
       </c>
       <c r="E31" t="str">
         <v/>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אבי בן ישראל - ברכה עליהם</v>
+        <v>איתי בירמן - אין אהבה ללא כאב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409347&amp;sid=4911af2243704a7b759f3f06503a8845</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409354&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אבי בן ישראל - ברכה עליהם</v>
+        <v>איתי בירמן - אין אהבה ללא כאב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>LioZee - הלב שלי אלייך</v>
+        <v>אור סלמן - מכתוב</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409346&amp;sid=4911af2243704a7b759f3f06503a8845</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409353&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-25</v>
@@ -507,12 +507,202 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>LioZee - הלב שלי אלייך</v>
+        <v>אור סלמן - מכתוב</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409352&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409351&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אבירם פרחן - נשמה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409350&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אבירם פרחן - נשמה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409349&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אבי לרנר - ותהי שמחה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409348&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-25</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אבי לרנר - ותהי שמחה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי בירמן - אין אהבה ללא כאב</v>
+        <v>שחר טבוך - טוק טו מי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409354&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409360&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי בירמן - אין אהבה ללא כאב</v>
+        <v>שחר טבוך - טוק טו מי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אור סלמן - מכתוב</v>
+        <v>נפתלי חיים - מחרוזת חופה 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409353&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409359&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-25</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אור סלמן - מכתוב</v>
+        <v>נפתלי חיים - מחרוזת חופה 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+        <v>יקיר יהודה יאיר - הולך איתי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409352&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409358&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-25</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אברהם איילאו &amp; אופק אדנק - מעגל</v>
+        <v>יקיר יהודה יאיר - הולך איתי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+        <v>יהונתן דרזי - לב שבור</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409351&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409357&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-25</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אבישי עוזיאל - מיטה ספוגה בדמעות</v>
+        <v>יהונתן דרזי - לב שבור</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אבירם פרחן - נשמה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409350&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409356&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-25</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אבירם פרחן - נשמה</v>
+        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
+        <v>בן אגם - ראש בראש</v>
       </c>
       <c r="B7" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409349&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409355&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
       </c>
       <c r="D7" t="str">
         <v>2026-01-25</v>
@@ -659,50 +659,12 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>אביב גפן &amp; ברי סחרוף - מנגינת הלב</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אבי לרנר - ותהי שמחה</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409348&amp;sid=db9290d6a92d2aea07f4f78064fb5bbd</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אבי לרנר - ותהי שמחה</v>
+        <v>בן אגם - ראש בראש</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שחר טבוך - טוק טו מי</v>
+        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-25</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409360&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409361&amp;sid=bb2b773653d416cfdab81cc6be2fe852</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-25</v>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שחר טבוך - טוק טו מי</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>נפתלי חיים - מחרוזת חופה 2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409359&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>נפתלי חיים - מחרוזת חופה 2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409358&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>יקיר יהודה יאיר - הולך איתי</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>יהונתן דרזי - לב שבור</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409357&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>יהונתן דרזי - לב שבור</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409356&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יהודה בורן &amp; נתנאל אמסילי - אילן קאבר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בן אגם - ראש בראש</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409355&amp;sid=b7a7b3545106de0938a1dbb945510b0d</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-25</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בן אגם - ראש בראש</v>
+        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
+        <v>שימי לנגא - שיר תודה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409361&amp;sid=bb2b773653d416cfdab81cc6be2fe852</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409370&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-25</v>
+        <v>2026-01-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יגל יובל שרעבי - סור מרע ועשה טוב</v>
+        <v>שימי לנגא - שיר תודה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רגב הוד - לירז</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409369&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רגב הוד - לירז</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>פן חזות - בואי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409368&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>פן חזות - בואי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409367&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ינון אליה - סך הכל ילדה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409366&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ינון אליה - סך הכל ילדה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>טלשי - עצוב לי שככה</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409365&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>טלשי - עצוב לי שככה</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>בצלאל שמיר - קרן אור</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409364&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>בצלאל שמיר - קרן אור</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אודי שניידר - מתחת למים</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409363&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-01-26</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אודי שניידר - מתחת למים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שימי לנגא - שיר תודה</v>
+        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409370&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409379&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שימי לנגא - שיר תודה</v>
+        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רגב הוד - לירז</v>
+        <v>יעל טאוב - קחי לך את הזמןת</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409369&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409378&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רגב הוד - לירז</v>
+        <v>יעל טאוב - קחי לך את הזמןת</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>פן חזות - בואי</v>
+        <v>ינון - להחזיק חזק</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409368&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409377&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>פן חזות - בואי</v>
+        <v>ינון - להחזיק חזק</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
+        <v>גיל אוליאל - רק עוד רגע</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409367&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409376&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>עופר לוי &amp; הגר יפת - חיים של אמא</v>
+        <v>גיל אוליאל - רק עוד רגע</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ינון אליה - סך הכל ילדה</v>
+        <v>בר סיידו - סיפור שנגמר</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409366&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409375&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ינון אליה - סך הכל ילדה</v>
+        <v>בר סיידו - סיפור שנגמר</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>טלשי - עצוב לי שככה</v>
+        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409365&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409373&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>טלשי - עצוב לי שככה</v>
+        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>בצלאל שמיר - קרן אור</v>
+        <v>אדיר גץ - זירת אגרוף</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409364&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409372&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>בצלאל שמיר - קרן אור</v>
+        <v>אדיר גץ - זירת אגרוף</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אודי שניידר - מתחת למים</v>
+        <v>אגם איזן - תעשי אהבה</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409363&amp;sid=eae9911b6505b4b3636087b09a75bd12</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409371&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-01-26</v>
+        <v>2026-01-27</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אודי שניידר - מתחת למים</v>
+        <v>אגם איזן - תעשי אהבה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-01-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
+        <v>שיר דוד גדסי - הִתְנַעַרְתִּי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409379&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409384&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-01-27</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נוי אביטל - מה מבקש להירפא הלילה</v>
+        <v>שיר דוד גדסי - הִתְנַעַרְתִּי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>יעל טאוב - קחי לך את הזמןת</v>
+        <v>עקיבא הירש פמנסקי - מחרוזת חתונות 2026</v>
       </c>
       <c r="B3" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409378&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409383&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D3" t="str">
         <v>2026-01-27</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>יעל טאוב - קחי לך את הזמןת</v>
+        <v>עקיבא הירש פמנסקי - מחרוזת חתונות 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ינון - להחזיק חזק</v>
+        <v>עמיר בניון - אות קין</v>
       </c>
       <c r="B4" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409377&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409382&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D4" t="str">
         <v>2026-01-27</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ינון - להחזיק חזק</v>
+        <v>עמיר בניון - אות קין</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גיל אוליאל - רק עוד רגע</v>
+        <v>עידן בקשי - נשיקות ושתיקות</v>
       </c>
       <c r="B5" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409376&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409381&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D5" t="str">
         <v>2026-01-27</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גיל אוליאל - רק עוד רגע</v>
+        <v>עידן בקשי - נשיקות ושתיקות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>בר סיידו - סיפור שנגמר</v>
+        <v>ניר אליאב - שבועיים בנפרד</v>
       </c>
       <c r="B6" t="str">
         <v>2026-01-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409375&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409380&amp;sid=aaae679c63a0fb8b7ff9fe33cb51fcb2</v>
       </c>
       <c r="D6" t="str">
         <v>2026-01-27</v>
@@ -621,126 +621,12 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>בר סיידו - סיפור שנגמר</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409373&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>בן שאשא &amp; שירה רווח - ניפגש במוצ''ש</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>אדיר גץ - זירת אגרוף</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409372&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>אדיר גץ - זירת אגרוף</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>אגם איזן - תעשי אהבה</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409371&amp;sid=0793a5f71c0836948f5e86de2cd6755d</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-01-27</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>אגם איזן - תעשי אהבה</v>
+        <v>ניר אליאב - שבועיים בנפרד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>